--- a/public/pro-novinare/veletrhy.xlsx
+++ b/public/pro-novinare/veletrhy.xlsx
@@ -4761,7 +4761,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Místo konání pořadatel pro letošní ročník zatím neuvedl; loni se akce konala v enteria areně.</t>
+          <t>Místo konání pořadatel pro ročník 2026 zatím neuvedl; v roce 2025 se akce konala v enteria areně.</t>
         </is>
       </c>
       <c r="L74" t="inlineStr"/>

--- a/public/pro-novinare/veletrhy.xlsx
+++ b/public/pro-novinare/veletrhy.xlsx
@@ -450,7 +450,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Stav k 2026-09-29. Obsahuje jen akce s potvrzeným termínem, tedy ověřeným na stránce pořadatele (79 akcí). Dalších 17 známých akcí na potvrzení termínu čeká.</t>
+          <t>Stav k 2026-09-30. Obsahuje jen akce s potvrzeným termínem, tedy ověřeným na stránce pořadatele (79 akcí). Dalších 17 známých akcí na potvrzení termínu čeká.</t>
         </is>
       </c>
     </row>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>akci_od_2026-09-29</t>
+          <t>akci_od_2026-09-30</t>
         </is>
       </c>
     </row>
